--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.210</t>
-  </si>
-  <si>
-    <t>(0.238)</t>
-  </si>
-  <si>
-    <t>5.645</t>
-  </si>
-  <si>
-    <t>(0.688)</t>
-  </si>
-  <si>
-    <t>14.081</t>
-  </si>
-  <si>
-    <t>(3.205)</t>
-  </si>
-  <si>
-    <t>19.653</t>
-  </si>
-  <si>
-    <t>(3.428)</t>
-  </si>
-  <si>
-    <t>1.231</t>
-  </si>
-  <si>
-    <t>(0.153)</t>
-  </si>
-  <si>
-    <t>7.753</t>
-  </si>
-  <si>
-    <t>(0.879)</t>
-  </si>
-  <si>
-    <t>2.578</t>
-  </si>
-  <si>
-    <t>(1.288)</t>
+    <t>1.094</t>
+  </si>
+  <si>
+    <t>(0.191)</t>
+  </si>
+  <si>
+    <t>5.876</t>
+  </si>
+  <si>
+    <t>(0.709)</t>
+  </si>
+  <si>
+    <t>12.045</t>
+  </si>
+  <si>
+    <t>(2.204)</t>
+  </si>
+  <si>
+    <t>16.265</t>
+  </si>
+  <si>
+    <t>(2.336)</t>
+  </si>
+  <si>
+    <t>1.273</t>
+  </si>
+  <si>
+    <t>(0.158)</t>
+  </si>
+  <si>
+    <t>8.079</t>
+  </si>
+  <si>
+    <t>(0.903)</t>
+  </si>
+  <si>
+    <t>1.301</t>
+  </si>
+  <si>
+    <t>(0.127)</t>
   </si>
   <si>
     <t>0.552</t>
   </si>
   <si>
-    <t>(0.087)</t>
-  </si>
-  <si>
-    <t>20.449</t>
-  </si>
-  <si>
-    <t>(2.920)</t>
-  </si>
-  <si>
-    <t>19.987</t>
-  </si>
-  <si>
-    <t>(4.862)</t>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>19.144</t>
+  </si>
+  <si>
+    <t>(2.379)</t>
+  </si>
+  <si>
+    <t>13.841</t>
+  </si>
+  <si>
+    <t>(2.441)</t>
   </si>
   <si>
     <t>21</t>
@@ -198,7 +198,7 @@
     <t>(8.744)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.208</t>
-  </si>
-  <si>
-    <t>-0.931</t>
-  </si>
-  <si>
-    <t>26.190***</t>
-  </si>
-  <si>
-    <t>26.779***</t>
-  </si>
-  <si>
-    <t>0.541</t>
-  </si>
-  <si>
-    <t>-1.038</t>
-  </si>
-  <si>
-    <t>-0.037</t>
-  </si>
-  <si>
-    <t>-0.124</t>
-  </si>
-  <si>
-    <t>36.662***</t>
-  </si>
-  <si>
-    <t>16.485</t>
+    <t>0.324</t>
+  </si>
+  <si>
+    <t>-1.162</t>
+  </si>
+  <si>
+    <t>28.227***</t>
+  </si>
+  <si>
+    <t>30.167***</t>
+  </si>
+  <si>
+    <t>0.499</t>
+  </si>
+  <si>
+    <t>-1.364</t>
+  </si>
+  <si>
+    <t>1.240***</t>
+  </si>
+  <si>
+    <t>-0.123</t>
+  </si>
+  <si>
+    <t>37.967***</t>
+  </si>
+  <si>
+    <t>22.632***</t>
   </si>
 </sst>
 </file>
